--- a/outputs/time_series_by_sensor/time_serie_fixsensor-m2_p1.xlsx
+++ b/outputs/time_series_by_sensor/time_serie_fixsensor-m2_p1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>E1-Aluno4</t>
+          <t>E1-Aluno5</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -533,7 +533,9 @@
       <c r="D6" t="n">
         <v>68.48712</v>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>60.51618</v>
+      </c>
       <c r="F6" t="n">
         <v>59.72872</v>
       </c>
@@ -553,7 +555,9 @@
       <c r="D7" t="n">
         <v>60.361233</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>61.639668</v>
+      </c>
       <c r="F7" t="n">
         <v>57.88749</v>
       </c>
@@ -573,7 +577,9 @@
       <c r="D8" t="n">
         <v>62.476627</v>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>61.16032</v>
+      </c>
       <c r="F8" t="n">
         <v>59.04748</v>
       </c>
@@ -593,7 +599,9 @@
       <c r="D9" t="n">
         <v>62.18171</v>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>65.76428</v>
+      </c>
       <c r="F9" t="n">
         <v>59.34916</v>
       </c>
@@ -613,7 +621,9 @@
       <c r="D10" t="n">
         <v>65.48272</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>60.653343</v>
+      </c>
       <c r="F10" t="n">
         <v>59.24923</v>
       </c>
@@ -633,7 +643,9 @@
       <c r="D11" t="n">
         <v>59.837395</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>59.783398</v>
+      </c>
       <c r="F11" t="n">
         <v>62.37871</v>
       </c>
@@ -653,7 +665,9 @@
       <c r="D12" t="n">
         <v>60.10208</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>60.56686</v>
+      </c>
       <c r="F12" t="n">
         <v>60.74127</v>
       </c>
@@ -673,7 +687,9 @@
       <c r="D13" t="n">
         <v>60.689213</v>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>61.56349</v>
+      </c>
       <c r="F13" t="n">
         <v>57.7873</v>
       </c>
@@ -693,7 +709,9 @@
       <c r="D14" t="n">
         <v>60.93337</v>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="n">
+        <v>61.824654</v>
+      </c>
       <c r="F14" t="n">
         <v>60.57583</v>
       </c>
@@ -713,7 +731,9 @@
       <c r="D15" t="n">
         <v>63.757156</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="n">
+        <v>64.965256</v>
+      </c>
       <c r="F15" t="n">
         <v>58.62745</v>
       </c>
@@ -733,7 +753,9 @@
       <c r="D16" t="n">
         <v>63.802395</v>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>60.76447</v>
+      </c>
       <c r="F16" t="n">
         <v>58.89177</v>
       </c>
@@ -753,7 +775,9 @@
       <c r="D17" t="n">
         <v>59.584602</v>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>59.603348</v>
+      </c>
       <c r="F17" t="n">
         <v>59.40289</v>
       </c>
@@ -773,7 +797,9 @@
       <c r="D18" t="n">
         <v>61.603775</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>61.937572</v>
+      </c>
       <c r="F18" t="n">
         <v>57.99395</v>
       </c>
@@ -793,7 +819,9 @@
       <c r="D19" t="n">
         <v>60.789974</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>59.54436</v>
+      </c>
       <c r="F19" t="n">
         <v>57.55899</v>
       </c>
@@ -813,7 +841,9 @@
       <c r="D20" t="n">
         <v>59.94992</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>60.609253</v>
+      </c>
       <c r="F20" t="n">
         <v>59.80473</v>
       </c>
@@ -833,7 +863,9 @@
       <c r="D21" t="n">
         <v>61.048397</v>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>60.84922</v>
+      </c>
       <c r="F21" t="n">
         <v>61.4208</v>
       </c>
@@ -853,7 +885,9 @@
       <c r="D22" t="n">
         <v>59.84497</v>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="n">
+        <v>59.37529</v>
+      </c>
       <c r="F22" t="n">
         <v>61.6473</v>
       </c>
@@ -873,7 +907,9 @@
       <c r="D23" t="n">
         <v>58.681183</v>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="n">
+        <v>59.84953</v>
+      </c>
       <c r="F23" t="n">
         <v>59.94909</v>
       </c>
@@ -893,7 +929,9 @@
       <c r="D24" t="n">
         <v>60.757866</v>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="n">
+        <v>61.791733</v>
+      </c>
       <c r="F24" t="n">
         <v>61.38485</v>
       </c>
@@ -913,7 +951,9 @@
       <c r="D25" t="n">
         <v>63.183414</v>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="n">
+        <v>62.9639</v>
+      </c>
       <c r="F25" t="n">
         <v>60.77596</v>
       </c>
@@ -933,7 +973,9 @@
       <c r="D26" t="n">
         <v>63.473362</v>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="n">
+        <v>62.238716</v>
+      </c>
       <c r="F26" t="n">
         <v>60.91581</v>
       </c>
@@ -953,7 +995,9 @@
       <c r="D27" t="n">
         <v>61.35799</v>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>62.052986</v>
+      </c>
       <c r="F27" t="n">
         <v>59.60978</v>
       </c>
@@ -973,7 +1017,9 @@
       <c r="D28" t="n">
         <v>62.782978</v>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>63.156845</v>
+      </c>
       <c r="F28" t="n">
         <v>57.88333</v>
       </c>
@@ -993,7 +1039,9 @@
       <c r="D29" t="n">
         <v>61.758526</v>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>62.23601</v>
+      </c>
       <c r="F29" t="n">
         <v>58.79396</v>
       </c>
@@ -1013,7 +1061,9 @@
       <c r="D30" t="n">
         <v>62.22611</v>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>62.888084</v>
+      </c>
       <c r="F30" t="n">
         <v>58.56301</v>
       </c>
@@ -1033,7 +1083,9 @@
       <c r="D31" t="n">
         <v>62.05268</v>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="n">
+        <v>60.440144</v>
+      </c>
       <c r="F31" t="n">
         <v>58.42174</v>
       </c>
@@ -1053,7 +1105,9 @@
       <c r="D32" t="n">
         <v>59.357204</v>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="n">
+        <v>59.825165</v>
+      </c>
       <c r="F32" t="n">
         <v>60.50537</v>
       </c>
@@ -1073,7 +1127,9 @@
       <c r="D33" t="n">
         <v>60.49365</v>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="n">
+        <v>60.27977</v>
+      </c>
       <c r="F33" t="n">
         <v>59.87341</v>
       </c>
@@ -1093,7 +1149,9 @@
       <c r="D34" t="n">
         <v>60.197</v>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="n">
+        <v>60.126026</v>
+      </c>
       <c r="F34" t="n">
         <v>58.34893</v>
       </c>
@@ -1113,7 +1171,9 @@
       <c r="D35" t="n">
         <v>59.489708</v>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="n">
+        <v>61.227814</v>
+      </c>
       <c r="F35" t="n">
         <v>58.65638</v>
       </c>
@@ -1133,7 +1193,9 @@
       <c r="D36" t="n">
         <v>62.186028</v>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="n">
+        <v>61.450275</v>
+      </c>
       <c r="F36" t="n">
         <v>57.93386</v>
       </c>
@@ -1153,7 +1215,9 @@
       <c r="D37" t="n">
         <v>61.649075</v>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="n">
+        <v>60.632217</v>
+      </c>
       <c r="F37" t="n">
         <v>56.93731</v>
       </c>
@@ -1173,7 +1237,9 @@
       <c r="D38" t="n">
         <v>60.09202</v>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="n">
+        <v>60.127937</v>
+      </c>
       <c r="F38" t="n">
         <v>58.13889</v>
       </c>
@@ -1193,7 +1259,9 @@
       <c r="D39" t="n">
         <v>60.357452</v>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="n">
+        <v>60.01591</v>
+      </c>
       <c r="F39" t="n">
         <v>57.18356</v>
       </c>
@@ -1213,7 +1281,9 @@
       <c r="D40" t="n">
         <v>60.196857</v>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>59.362583</v>
+      </c>
       <c r="F40" t="n">
         <v>58.11441</v>
       </c>
@@ -1233,7 +1303,9 @@
       <c r="D41" t="n">
         <v>58.741474</v>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>59.492176</v>
+      </c>
       <c r="F41" t="n">
         <v>58.39024</v>
       </c>
@@ -1253,7 +1325,9 @@
       <c r="D42" t="n">
         <v>60.87088</v>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>59.289032</v>
+      </c>
       <c r="F42" t="n">
         <v>59.2405</v>
       </c>
@@ -1273,7 +1347,9 @@
       <c r="D43" t="n">
         <v>59.583675</v>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="n">
+        <v>59.255142</v>
+      </c>
       <c r="F43" t="n">
         <v>60.48279</v>
       </c>
@@ -1293,7 +1369,9 @@
       <c r="D44" t="n">
         <v>60.362965</v>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="n">
+        <v>60.176483</v>
+      </c>
       <c r="F44" t="n">
         <v>59.83413</v>
       </c>
@@ -1313,7 +1391,9 @@
       <c r="D45" t="n">
         <v>59.99293</v>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="n">
+        <v>60.327938</v>
+      </c>
       <c r="F45" t="n">
         <v>65.90797000000001</v>
       </c>
@@ -1333,7 +1413,9 @@
       <c r="D46" t="n">
         <v>60.662395</v>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>61.14664</v>
+      </c>
       <c r="F46" t="n">
         <v>60.96604</v>
       </c>
@@ -1353,7 +1435,9 @@
       <c r="D47" t="n">
         <v>62.075443</v>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="n">
+        <v>62.686802</v>
+      </c>
       <c r="F47" t="n">
         <v>59.1661</v>
       </c>
@@ -1373,7 +1457,9 @@
       <c r="D48" t="n">
         <v>61.809444</v>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>61.209854</v>
+      </c>
       <c r="F48" t="n">
         <v>60.08152</v>
       </c>
@@ -1393,7 +1479,9 @@
       <c r="D49" t="n">
         <v>61.59531</v>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="n">
+        <v>71.535545</v>
+      </c>
       <c r="F49" t="n">
         <v>58.92231</v>
       </c>
@@ -1413,7 +1501,9 @@
       <c r="D50" t="n">
         <v>74.398476</v>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>61.673565</v>
+      </c>
       <c r="F50" t="n">
         <v>59.67399</v>
       </c>
@@ -1433,7 +1523,9 @@
       <c r="D51" t="n">
         <v>61.112934</v>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="n">
+        <v>61.778446</v>
+      </c>
       <c r="F51" t="n">
         <v>58.89618</v>
       </c>
@@ -1453,7 +1545,9 @@
       <c r="D52" t="n">
         <v>64.55932</v>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="n">
+        <v>61.381226</v>
+      </c>
       <c r="F52" t="n">
         <v>57.78743</v>
       </c>
@@ -1473,7 +1567,9 @@
       <c r="D53" t="n">
         <v>62.02808</v>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>60.540985</v>
+      </c>
       <c r="F53" t="n">
         <v>58.48761</v>
       </c>
@@ -1493,7 +1589,9 @@
       <c r="D54" t="n">
         <v>62.6793</v>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="n">
+        <v>62.933315</v>
+      </c>
       <c r="F54" t="n">
         <v>60.09832</v>
       </c>
@@ -1513,7 +1611,9 @@
       <c r="D55" t="n">
         <v>61.059628</v>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="n">
+        <v>64.32601</v>
+      </c>
       <c r="F55" t="n">
         <v>60.10777</v>
       </c>
@@ -1533,7 +1633,9 @@
       <c r="D56" t="n">
         <v>60.171505</v>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>61.02605</v>
+      </c>
       <c r="F56" t="n">
         <v>60.09011</v>
       </c>
@@ -1553,7 +1655,9 @@
       <c r="D57" t="n">
         <v>61.788628</v>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>62.829945</v>
+      </c>
       <c r="F57" t="n">
         <v>59.84391</v>
       </c>
@@ -1573,7 +1677,9 @@
       <c r="D58" t="n">
         <v>61.048912</v>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="n">
+        <v>62.604965</v>
+      </c>
       <c r="F58" t="n">
         <v>59.17297</v>
       </c>
@@ -1593,7 +1699,9 @@
       <c r="D59" t="n">
         <v>63.469048</v>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>61.92176</v>
+      </c>
       <c r="F59" t="n">
         <v>61.75933</v>
       </c>
@@ -1613,7 +1721,9 @@
       <c r="D60" t="n">
         <v>61.61558</v>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="n">
+        <v>62.283592</v>
+      </c>
       <c r="F60" t="n">
         <v>61.86197</v>
       </c>
@@ -1633,7 +1743,9 @@
       <c r="D61" t="n">
         <v>62.585728</v>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="n">
+        <v>61.78614</v>
+      </c>
       <c r="F61" t="n">
         <v>61.44333</v>
       </c>
@@ -1653,7 +1765,9 @@
       <c r="D62" t="n">
         <v>62.496704</v>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="n">
+        <v>61.418224</v>
+      </c>
       <c r="F62" t="n">
         <v>60.18489</v>
       </c>
@@ -1673,7 +1787,9 @@
       <c r="D63" t="n">
         <v>63.044365</v>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>64.37903</v>
+      </c>
       <c r="F63" t="n">
         <v>61.71914</v>
       </c>
@@ -1689,7 +1805,9 @@
       <c r="D64" t="n">
         <v>64.48718</v>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="n">
+        <v>63.82497</v>
+      </c>
       <c r="F64" t="n">
         <v>60.26675</v>
       </c>
@@ -1705,7 +1823,9 @@
       <c r="D65" t="n">
         <v>64.1507</v>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="n">
+        <v>63.84064</v>
+      </c>
       <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -1719,1126 +1839,36 @@
       <c r="D66" t="n">
         <v>62.55494</v>
       </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="n">
+        <v>62.683365</v>
+      </c>
       <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>14:49:51</t>
+          <t>14:49:48</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>63.089436</v>
+      </c>
       <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>16:20:03</t>
+          <t>14:49:51</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="n">
-        <v>64.01926400000001</v>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>16:20:04</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="n">
-        <v>63.28522</v>
-      </c>
-      <c r="F69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>16:20:05</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="n">
-        <v>67.55947</v>
-      </c>
-      <c r="F70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>16:20:06</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="n">
-        <v>81.36927</v>
-      </c>
-      <c r="F71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>16:20:07</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="n">
-        <v>65.287796</v>
-      </c>
-      <c r="F72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>16:20:08</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="n">
-        <v>69.55784</v>
-      </c>
-      <c r="F73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>16:20:09</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="n">
-        <v>75.46071999999999</v>
-      </c>
-      <c r="F74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>16:20:10</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="n">
-        <v>65.28116</v>
-      </c>
-      <c r="F75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>16:20:11</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="n">
-        <v>65.22047999999999</v>
-      </c>
-      <c r="F76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>16:20:12</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="n">
-        <v>68.10509500000001</v>
-      </c>
-      <c r="F77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>16:20:13</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="n">
-        <v>66.06545</v>
-      </c>
-      <c r="F78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>16:20:14</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="n">
-        <v>66.76261</v>
-      </c>
-      <c r="F79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>16:20:15</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="n">
-        <v>66.485664</v>
-      </c>
-      <c r="F80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>16:20:16</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="n">
-        <v>64.986244</v>
-      </c>
-      <c r="F81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>16:20:17</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="n">
-        <v>64.13389599999999</v>
-      </c>
-      <c r="F82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>16:20:18</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="n">
-        <v>64.645454</v>
-      </c>
-      <c r="F83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>16:20:19</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="n">
-        <v>63.45288</v>
-      </c>
-      <c r="F84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>16:20:20</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="n">
-        <v>65.2236</v>
-      </c>
-      <c r="F85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>16:20:21</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="n">
-        <v>64.22683000000001</v>
-      </c>
-      <c r="F86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>16:20:22</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="n">
-        <v>66.14167999999999</v>
-      </c>
-      <c r="F87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>16:20:23</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="n">
-        <v>65.92263</v>
-      </c>
-      <c r="F88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>16:20:24</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="n">
-        <v>66.47566</v>
-      </c>
-      <c r="F89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>16:20:25</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="n">
-        <v>66.449265</v>
-      </c>
-      <c r="F90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>16:20:26</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="n">
-        <v>65.35045</v>
-      </c>
-      <c r="F91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>16:20:27</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="n">
-        <v>64.31806</v>
-      </c>
-      <c r="F92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>16:20:28</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="n">
-        <v>64.19825</v>
-      </c>
-      <c r="F93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>16:20:29</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="n">
-        <v>65.41701</v>
-      </c>
-      <c r="F94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>16:20:30</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="n">
-        <v>63.939</v>
-      </c>
-      <c r="F95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>16:20:31</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="n">
-        <v>63.56778</v>
-      </c>
-      <c r="F96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>16:20:32</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="n">
-        <v>65.92187</v>
-      </c>
-      <c r="F97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>16:20:33</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="n">
-        <v>66.43643</v>
-      </c>
-      <c r="F98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>16:20:34</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
-      <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="n">
-        <v>66.070435</v>
-      </c>
-      <c r="F99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>16:20:35</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="n">
-        <v>65.00613</v>
-      </c>
-      <c r="F100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>16:20:36</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="n">
-        <v>63.600624</v>
-      </c>
-      <c r="F101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>16:20:37</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
-      <c r="C102" t="inlineStr"/>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="n">
-        <v>62.848686</v>
-      </c>
-      <c r="F102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>16:20:38</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="n">
-        <v>63.076187</v>
-      </c>
-      <c r="F103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>16:20:39</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="n">
-        <v>63.18382</v>
-      </c>
-      <c r="F104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>16:20:40</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="n">
-        <v>62.65964</v>
-      </c>
-      <c r="F105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>16:20:41</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="n">
-        <v>62.373848</v>
-      </c>
-      <c r="F106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>16:20:42</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
-      <c r="C107" t="inlineStr"/>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="n">
-        <v>62.818382</v>
-      </c>
-      <c r="F107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>16:20:43</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="n">
-        <v>66.303856</v>
-      </c>
-      <c r="F108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>16:20:44</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="n">
-        <v>67.86759000000001</v>
-      </c>
-      <c r="F109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>16:20:45</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="n">
-        <v>67.51797000000001</v>
-      </c>
-      <c r="F110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>16:20:46</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr"/>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="n">
-        <v>65.46023599999999</v>
-      </c>
-      <c r="F111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>16:20:47</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr"/>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="n">
-        <v>63.66899</v>
-      </c>
-      <c r="F112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>16:20:48</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="n">
-        <v>66.31117999999999</v>
-      </c>
-      <c r="F113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>16:20:49</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="n">
-        <v>65.399765</v>
-      </c>
-      <c r="F114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>16:20:50</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr"/>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="n">
-        <v>65.308266</v>
-      </c>
-      <c r="F115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>16:20:51</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="n">
-        <v>64.79301</v>
-      </c>
-      <c r="F116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>16:20:52</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr"/>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="n">
-        <v>63.811825</v>
-      </c>
-      <c r="F117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>16:20:53</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="n">
-        <v>63.585236</v>
-      </c>
-      <c r="F118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>16:20:54</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="n">
-        <v>63.43199</v>
-      </c>
-      <c r="F119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>16:20:55</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr"/>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="n">
-        <v>63.257313</v>
-      </c>
-      <c r="F120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>16:20:56</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" t="n">
-        <v>63.91938</v>
-      </c>
-      <c r="F121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>16:20:57</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="n">
-        <v>65.702</v>
-      </c>
-      <c r="F122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>16:20:58</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="n">
-        <v>63.522694</v>
-      </c>
-      <c r="F123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>16:20:59</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
-      <c r="C124" t="inlineStr"/>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="n">
-        <v>64.14812999999999</v>
-      </c>
-      <c r="F124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>16:21:00</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
-      <c r="C125" t="inlineStr"/>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="n">
-        <v>63.817448</v>
-      </c>
-      <c r="F125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>16:21:01</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
-      <c r="C126" t="inlineStr"/>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="n">
-        <v>62.09636</v>
-      </c>
-      <c r="F126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>16:21:02</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="n">
-        <v>63.609676</v>
-      </c>
-      <c r="F127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>16:21:03</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="n">
-        <v>63.507126</v>
-      </c>
-      <c r="F128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>16:21:04</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
-      <c r="C129" t="inlineStr"/>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="n">
-        <v>64.41939000000001</v>
-      </c>
-      <c r="F129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>16:21:05</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr"/>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="n">
-        <v>63.66633</v>
-      </c>
-      <c r="F130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>16:21:06</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
-      <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="n">
-        <v>62.618477</v>
-      </c>
-      <c r="F131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>16:21:07</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
-      <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="n">
-        <v>63.07851</v>
-      </c>
-      <c r="F132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>16:21:08</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr"/>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="n">
-        <v>62.9655</v>
-      </c>
-      <c r="F133" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>16:21:09</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
-      <c r="C134" t="inlineStr"/>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="n">
-        <v>64.38683</v>
-      </c>
-      <c r="F134" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>16:21:10</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="n">
-        <v>63.25656</v>
-      </c>
-      <c r="F135" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>16:21:11</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" t="n">
-        <v>63.21534</v>
-      </c>
-      <c r="F136" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>16:21:12</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr"/>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="n">
-        <v>63.274403</v>
-      </c>
-      <c r="F137" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>16:21:13</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="n">
-        <v>62.699368</v>
-      </c>
-      <c r="F138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>16:21:14</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="n">
-        <v>63.443314</v>
-      </c>
-      <c r="F139" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>16:21:15</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
-      <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="n">
-        <v>61.963253</v>
-      </c>
-      <c r="F140" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>16:21:16</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr"/>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="n">
-        <v>64.12285</v>
-      </c>
-      <c r="F141" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>16:21:17</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="n">
-        <v>65.50606500000001</v>
-      </c>
-      <c r="F142" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>16:21:18</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="n">
-        <v>64.46507</v>
-      </c>
-      <c r="F143" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>16:21:19</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="n">
-        <v>65.76758599999999</v>
-      </c>
-      <c r="F144" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>16:21:20</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr"/>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="n">
-        <v>65.71832999999999</v>
-      </c>
-      <c r="F145" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>16:21:21</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
-      <c r="C146" t="inlineStr"/>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="n">
-        <v>66.10767</v>
-      </c>
-      <c r="F146" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
